--- a/raw/processedSamples/20260519_r13_CMH_USDA-blood_Nano-QuIC.xlsx
+++ b/raw/processedSamples/20260519_r13_CMH_USDA-blood_Nano-QuIC.xlsx
@@ -5,17 +5,16 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mnpro\Desktop\RT-QuIC Data\Caylie\20260519_r13_CMH_USDA-blood_Nano-QuIC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rowde002\Documents\Projects\usda-validation\raw\processedSamples\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15E71CC3-3E0F-4F03-A8B7-092A1F06AD06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F16A9CF-43B0-45E0-851C-66353E54AEEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4935" yWindow="1200" windowWidth="23730" windowHeight="13170" activeTab="2" xr2:uid="{F8DBAC4F-C712-4491-AA09-EB5717C4C264}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F8DBAC4F-C712-4491-AA09-EB5717C4C264}"/>
   </bookViews>
   <sheets>
     <sheet name="Microplate Time 1 (0 h)" sheetId="2" r:id="rId1"/>
     <sheet name="Table All Data points" sheetId="1" r:id="rId2"/>
-    <sheet name="Curves" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -853,55 +852,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>24</xdr:col>
-      <xdr:colOff>150552</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>85167</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AAAF5956-20A0-F0C1-2F13-709358DEA661}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="14780952" cy="4466667"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -1695,37 +1645,37 @@
         <v>1000</v>
       </c>
       <c r="C27" s="12">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="D27" s="12">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="E27" s="12">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="F27" s="12">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="G27" s="12">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="H27" s="12">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="I27" s="12">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="J27" s="12">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="K27" s="12">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="L27" s="12">
-        <v>100</v>
-      </c>
-      <c r="M27" s="13">
-        <v>100</v>
+        <v>4</v>
+      </c>
+      <c r="M27" s="12">
+        <v>4</v>
       </c>
       <c r="O27" s="21"/>
     </row>
@@ -1736,38 +1686,38 @@
       <c r="B28" s="5">
         <v>1000</v>
       </c>
-      <c r="C28" s="14">
-        <v>100</v>
-      </c>
-      <c r="D28" s="14">
-        <v>100</v>
-      </c>
-      <c r="E28" s="14">
-        <v>100</v>
-      </c>
-      <c r="F28" s="14">
-        <v>100</v>
-      </c>
-      <c r="G28" s="14">
-        <v>100</v>
-      </c>
-      <c r="H28" s="14">
-        <v>100</v>
-      </c>
-      <c r="I28" s="14">
-        <v>100</v>
-      </c>
-      <c r="J28" s="14">
-        <v>100</v>
-      </c>
-      <c r="K28" s="14">
-        <v>100</v>
-      </c>
-      <c r="L28" s="14">
-        <v>100</v>
-      </c>
-      <c r="M28" s="15">
-        <v>100</v>
+      <c r="C28" s="12">
+        <v>4</v>
+      </c>
+      <c r="D28" s="12">
+        <v>4</v>
+      </c>
+      <c r="E28" s="12">
+        <v>4</v>
+      </c>
+      <c r="F28" s="12">
+        <v>4</v>
+      </c>
+      <c r="G28" s="12">
+        <v>4</v>
+      </c>
+      <c r="H28" s="12">
+        <v>4</v>
+      </c>
+      <c r="I28" s="12">
+        <v>4</v>
+      </c>
+      <c r="J28" s="12">
+        <v>4</v>
+      </c>
+      <c r="K28" s="12">
+        <v>4</v>
+      </c>
+      <c r="L28" s="12">
+        <v>4</v>
+      </c>
+      <c r="M28" s="12">
+        <v>4</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
@@ -1777,38 +1727,38 @@
       <c r="B29" s="5">
         <v>1000</v>
       </c>
-      <c r="C29" s="14">
-        <v>100</v>
-      </c>
-      <c r="D29" s="14">
-        <v>100</v>
-      </c>
-      <c r="E29" s="14">
-        <v>100</v>
-      </c>
-      <c r="F29" s="14">
-        <v>100</v>
-      </c>
-      <c r="G29" s="14">
-        <v>100</v>
-      </c>
-      <c r="H29" s="14">
-        <v>100</v>
-      </c>
-      <c r="I29" s="14">
-        <v>100</v>
-      </c>
-      <c r="J29" s="14">
-        <v>100</v>
-      </c>
-      <c r="K29" s="14">
-        <v>100</v>
-      </c>
-      <c r="L29" s="14">
-        <v>100</v>
-      </c>
-      <c r="M29" s="15">
-        <v>100</v>
+      <c r="C29" s="12">
+        <v>4</v>
+      </c>
+      <c r="D29" s="12">
+        <v>4</v>
+      </c>
+      <c r="E29" s="12">
+        <v>4</v>
+      </c>
+      <c r="F29" s="12">
+        <v>4</v>
+      </c>
+      <c r="G29" s="12">
+        <v>4</v>
+      </c>
+      <c r="H29" s="12">
+        <v>4</v>
+      </c>
+      <c r="I29" s="12">
+        <v>4</v>
+      </c>
+      <c r="J29" s="12">
+        <v>4</v>
+      </c>
+      <c r="K29" s="12">
+        <v>4</v>
+      </c>
+      <c r="L29" s="12">
+        <v>4</v>
+      </c>
+      <c r="M29" s="12">
+        <v>4</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
@@ -1818,38 +1768,38 @@
       <c r="B30" s="5">
         <v>1000</v>
       </c>
-      <c r="C30" s="14">
-        <v>100</v>
-      </c>
-      <c r="D30" s="14">
-        <v>100</v>
-      </c>
-      <c r="E30" s="14">
-        <v>100</v>
-      </c>
-      <c r="F30" s="14">
-        <v>100</v>
-      </c>
-      <c r="G30" s="14">
-        <v>100</v>
-      </c>
-      <c r="H30" s="14">
-        <v>100</v>
-      </c>
-      <c r="I30" s="14">
-        <v>100</v>
-      </c>
-      <c r="J30" s="14">
-        <v>100</v>
-      </c>
-      <c r="K30" s="14">
-        <v>100</v>
-      </c>
-      <c r="L30" s="14">
-        <v>100</v>
-      </c>
-      <c r="M30" s="15">
-        <v>100</v>
+      <c r="C30" s="12">
+        <v>4</v>
+      </c>
+      <c r="D30" s="12">
+        <v>4</v>
+      </c>
+      <c r="E30" s="12">
+        <v>4</v>
+      </c>
+      <c r="F30" s="12">
+        <v>4</v>
+      </c>
+      <c r="G30" s="12">
+        <v>4</v>
+      </c>
+      <c r="H30" s="12">
+        <v>4</v>
+      </c>
+      <c r="I30" s="12">
+        <v>4</v>
+      </c>
+      <c r="J30" s="12">
+        <v>4</v>
+      </c>
+      <c r="K30" s="12">
+        <v>4</v>
+      </c>
+      <c r="L30" s="12">
+        <v>4</v>
+      </c>
+      <c r="M30" s="12">
+        <v>4</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
@@ -1859,38 +1809,38 @@
       <c r="B31" s="5">
         <v>1000</v>
       </c>
-      <c r="C31" s="14">
-        <v>100</v>
-      </c>
-      <c r="D31" s="14">
-        <v>100</v>
-      </c>
-      <c r="E31" s="14">
-        <v>100</v>
-      </c>
-      <c r="F31" s="14">
-        <v>100</v>
-      </c>
-      <c r="G31" s="14">
-        <v>100</v>
-      </c>
-      <c r="H31" s="14">
-        <v>100</v>
-      </c>
-      <c r="I31" s="14">
-        <v>100</v>
-      </c>
-      <c r="J31" s="14">
-        <v>100</v>
-      </c>
-      <c r="K31" s="14">
-        <v>100</v>
-      </c>
-      <c r="L31" s="14">
-        <v>100</v>
-      </c>
-      <c r="M31" s="15">
-        <v>100</v>
+      <c r="C31" s="12">
+        <v>4</v>
+      </c>
+      <c r="D31" s="12">
+        <v>4</v>
+      </c>
+      <c r="E31" s="12">
+        <v>4</v>
+      </c>
+      <c r="F31" s="12">
+        <v>4</v>
+      </c>
+      <c r="G31" s="12">
+        <v>4</v>
+      </c>
+      <c r="H31" s="12">
+        <v>4</v>
+      </c>
+      <c r="I31" s="12">
+        <v>4</v>
+      </c>
+      <c r="J31" s="12">
+        <v>4</v>
+      </c>
+      <c r="K31" s="12">
+        <v>4</v>
+      </c>
+      <c r="L31" s="12">
+        <v>4</v>
+      </c>
+      <c r="M31" s="12">
+        <v>4</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
@@ -1900,38 +1850,38 @@
       <c r="B32" s="5">
         <v>1000</v>
       </c>
-      <c r="C32" s="14">
-        <v>100</v>
-      </c>
-      <c r="D32" s="14">
-        <v>100</v>
-      </c>
-      <c r="E32" s="14">
-        <v>100</v>
-      </c>
-      <c r="F32" s="14">
-        <v>100</v>
-      </c>
-      <c r="G32" s="14">
-        <v>100</v>
-      </c>
-      <c r="H32" s="14">
-        <v>100</v>
-      </c>
-      <c r="I32" s="14">
-        <v>100</v>
-      </c>
-      <c r="J32" s="14">
-        <v>100</v>
-      </c>
-      <c r="K32" s="14">
-        <v>100</v>
-      </c>
-      <c r="L32" s="14">
-        <v>100</v>
-      </c>
-      <c r="M32" s="15">
-        <v>100</v>
+      <c r="C32" s="12">
+        <v>4</v>
+      </c>
+      <c r="D32" s="12">
+        <v>4</v>
+      </c>
+      <c r="E32" s="12">
+        <v>4</v>
+      </c>
+      <c r="F32" s="12">
+        <v>4</v>
+      </c>
+      <c r="G32" s="12">
+        <v>4</v>
+      </c>
+      <c r="H32" s="12">
+        <v>4</v>
+      </c>
+      <c r="I32" s="12">
+        <v>4</v>
+      </c>
+      <c r="J32" s="12">
+        <v>4</v>
+      </c>
+      <c r="K32" s="12">
+        <v>4</v>
+      </c>
+      <c r="L32" s="12">
+        <v>4</v>
+      </c>
+      <c r="M32" s="12">
+        <v>4</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
@@ -1941,38 +1891,38 @@
       <c r="B33" s="5">
         <v>1000</v>
       </c>
-      <c r="C33" s="14">
-        <v>100</v>
-      </c>
-      <c r="D33" s="14">
-        <v>100</v>
-      </c>
-      <c r="E33" s="14">
-        <v>100</v>
-      </c>
-      <c r="F33" s="14">
-        <v>100</v>
-      </c>
-      <c r="G33" s="14">
-        <v>100</v>
-      </c>
-      <c r="H33" s="14">
-        <v>100</v>
-      </c>
-      <c r="I33" s="14">
-        <v>100</v>
-      </c>
-      <c r="J33" s="14">
-        <v>100</v>
-      </c>
-      <c r="K33" s="14">
-        <v>100</v>
-      </c>
-      <c r="L33" s="14">
-        <v>100</v>
-      </c>
-      <c r="M33" s="15">
-        <v>100</v>
+      <c r="C33" s="12">
+        <v>4</v>
+      </c>
+      <c r="D33" s="12">
+        <v>4</v>
+      </c>
+      <c r="E33" s="12">
+        <v>4</v>
+      </c>
+      <c r="F33" s="12">
+        <v>4</v>
+      </c>
+      <c r="G33" s="12">
+        <v>4</v>
+      </c>
+      <c r="H33" s="12">
+        <v>4</v>
+      </c>
+      <c r="I33" s="12">
+        <v>4</v>
+      </c>
+      <c r="J33" s="12">
+        <v>4</v>
+      </c>
+      <c r="K33" s="12">
+        <v>4</v>
+      </c>
+      <c r="L33" s="12">
+        <v>4</v>
+      </c>
+      <c r="M33" s="12">
+        <v>4</v>
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
@@ -1982,38 +1932,38 @@
       <c r="B34" s="16">
         <v>1000</v>
       </c>
-      <c r="C34" s="17">
-        <v>100</v>
-      </c>
-      <c r="D34" s="17">
-        <v>100</v>
-      </c>
-      <c r="E34" s="17">
-        <v>100</v>
-      </c>
-      <c r="F34" s="17">
-        <v>100</v>
-      </c>
-      <c r="G34" s="17">
-        <v>100</v>
-      </c>
-      <c r="H34" s="17">
-        <v>100</v>
-      </c>
-      <c r="I34" s="17">
-        <v>100</v>
-      </c>
-      <c r="J34" s="17">
-        <v>100</v>
-      </c>
-      <c r="K34" s="17">
-        <v>100</v>
-      </c>
-      <c r="L34" s="17">
-        <v>100</v>
-      </c>
-      <c r="M34" s="18">
-        <v>100</v>
+      <c r="C34" s="12">
+        <v>4</v>
+      </c>
+      <c r="D34" s="12">
+        <v>4</v>
+      </c>
+      <c r="E34" s="12">
+        <v>4</v>
+      </c>
+      <c r="F34" s="12">
+        <v>4</v>
+      </c>
+      <c r="G34" s="12">
+        <v>4</v>
+      </c>
+      <c r="H34" s="12">
+        <v>4</v>
+      </c>
+      <c r="I34" s="12">
+        <v>4</v>
+      </c>
+      <c r="J34" s="12">
+        <v>4</v>
+      </c>
+      <c r="K34" s="12">
+        <v>4</v>
+      </c>
+      <c r="L34" s="12">
+        <v>4</v>
+      </c>
+      <c r="M34" s="12">
+        <v>4</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
@@ -89168,18 +89118,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7D049BA-572B-45B0-85B8-F085BAB4F858}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="39" orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
-</worksheet>
 </file>